--- a/imports/SOP.xlsx
+++ b/imports/SOP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Limpieza\LIMPIEZA_APP\sop_lavado_app\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CAB2543-A73B-4B58-B996-83C5B5CC4C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA44BB4E-0291-4343-86D9-845C03181073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" activeTab="2" xr2:uid="{B8AE8316-DE00-4F18-9EBC-F49DAD0CC8B9}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="162">
   <si>
     <t>BD</t>
   </si>
@@ -418,9 +418,6 @@
     <t>ES-AD-DI-BA-001-SP-001-P</t>
   </si>
   <si>
-    <t>ES-AD-DI-BA-001-VI-001-P</t>
-  </si>
-  <si>
     <t>ES-AD-DI-BA-001-TL-001-B</t>
   </si>
   <si>
@@ -511,9 +508,6 @@
     <t>ES-AD-DI-OF-001-SP-001-P</t>
   </si>
   <si>
-    <t>ES-AD-DI-OF-001-VI-001-P</t>
-  </si>
-  <si>
     <t>ES-AD-DI-OF-001-SA-001-B</t>
   </si>
   <si>
@@ -521,6 +515,15 @@
   </si>
   <si>
     <t>ES-AD-DI-OF-001-SA-001-P</t>
+  </si>
+  <si>
+    <t>KT-VI-001</t>
+  </si>
+  <si>
+    <t>RE-VI-001</t>
+  </si>
+  <si>
+    <t>CM-DS-002</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1970,7 @@
     </row>
     <row r="11" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>17</v>
@@ -2017,7 +2020,7 @@
     </row>
     <row r="12" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>17</v>
@@ -2067,7 +2070,7 @@
     </row>
     <row r="13" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>17</v>
@@ -2111,7 +2114,7 @@
     </row>
     <row r="14" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>17</v>
@@ -2155,13 +2158,13 @@
     </row>
     <row r="15" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -2194,12 +2197,12 @@
         <v>100</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>17</v>
@@ -2243,7 +2246,7 @@
     </row>
     <row r="17" spans="1:14" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>17</v>
@@ -2824,12 +2827,16 @@
       <c r="C10" s="4">
         <v>3</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="H10" s="4">
         <v>10</v>
       </c>
@@ -3051,7 +3058,7 @@
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="4">
@@ -3107,7 +3114,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="4">
@@ -3163,7 +3170,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="4">
@@ -3550,10 +3557,10 @@
     </row>
     <row r="23" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="4">
         <v>1</v>
@@ -3606,10 +3613,10 @@
     </row>
     <row r="24" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C24" s="4">
         <v>2</v>
@@ -3662,10 +3669,10 @@
     </row>
     <row r="25" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C25" s="4">
         <v>3</v>
@@ -3718,10 +3725,10 @@
     </row>
     <row r="26" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
@@ -3772,10 +3779,10 @@
     </row>
     <row r="27" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C27" s="4">
         <v>2</v>
@@ -3826,10 +3833,10 @@
     </row>
     <row r="28" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C28" s="4">
         <v>3</v>
@@ -3886,10 +3893,10 @@
     </row>
     <row r="29" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C29" s="4">
         <v>3</v>
@@ -3897,7 +3904,7 @@
       <c r="D29" s="4"/>
       <c r="E29" s="7"/>
       <c r="F29" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="4">
@@ -3942,20 +3949,24 @@
     </row>
     <row r="30" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C30" s="4">
         <v>3</v>
       </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G30" s="7"/>
+      <c r="D30" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="H30" s="4">
         <v>10</v>
       </c>
@@ -3998,10 +4009,10 @@
     </row>
     <row r="31" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="4">
         <v>1</v>
@@ -4009,7 +4020,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="4">
@@ -4046,7 +4057,7 @@
         <v>100</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T31" s="9" t="s">
         <v>121</v>
@@ -4054,10 +4065,10 @@
     </row>
     <row r="32" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C32" s="4">
         <v>2</v>
@@ -4065,7 +4076,7 @@
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
       <c r="F32" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="4">
@@ -4102,7 +4113,7 @@
         <v>100</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T32" s="4" t="s">
         <v>122</v>
@@ -4110,10 +4121,10 @@
     </row>
     <row r="33" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C33" s="4">
         <v>3</v>
@@ -4121,7 +4132,7 @@
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="4">
@@ -4158,7 +4169,7 @@
         <v>100</v>
       </c>
       <c r="S33" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="T33" s="4" t="s">
         <v>123</v>
@@ -4166,10 +4177,10 @@
     </row>
     <row r="34" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
@@ -4222,10 +4233,10 @@
     </row>
     <row r="35" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C35" s="4">
         <v>2</v>
@@ -4278,10 +4289,10 @@
     </row>
     <row r="36" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C36" s="4">
         <v>3</v>
@@ -4334,10 +4345,10 @@
     </row>
     <row r="37" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C37" s="4">
         <v>1</v>
@@ -4394,10 +4405,10 @@
     </row>
     <row r="38" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C38" s="4">
         <v>2</v>
@@ -4454,10 +4465,10 @@
     </row>
     <row r="39" spans="1:20" ht="28.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C39" s="4">
         <v>3</v>
